--- a/data/nzd0047/nzd0047.xlsx
+++ b/data/nzd0047/nzd0047.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D523"/>
+  <dimension ref="A1:D528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9844,6 +9844,96 @@
         <v>406.76</v>
       </c>
       <c r="D523" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>413.28</v>
+      </c>
+      <c r="C524" t="n">
+        <v>408.66</v>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>413.76</v>
+      </c>
+      <c r="C525" t="n">
+        <v>409.53</v>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>413.61</v>
+      </c>
+      <c r="C526" t="n">
+        <v>410.12</v>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>414.12</v>
+      </c>
+      <c r="C527" t="n">
+        <v>411.26</v>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>413.65</v>
+      </c>
+      <c r="C528" t="n">
+        <v>411.17</v>
+      </c>
+      <c r="D528" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9860,7 +9950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B638"/>
+  <dimension ref="A1:B643"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16243,6 +16333,56 @@
       </c>
       <c r="B638" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>
@@ -16411,28 +16551,28 @@
         <v>0.1827</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2126828399452503</v>
+        <v>0.2575700644642678</v>
       </c>
       <c r="J2" t="n">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="K2" t="n">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02592225368191359</v>
+        <v>0.03586892366319272</v>
       </c>
       <c r="M2" t="n">
-        <v>8.907523471412429</v>
+        <v>9.11578753087074</v>
       </c>
       <c r="N2" t="n">
-        <v>110.8600434252092</v>
+        <v>117.2519019826536</v>
       </c>
       <c r="O2" t="n">
-        <v>10.5290096127418</v>
+        <v>10.82829173889647</v>
       </c>
       <c r="P2" t="n">
-        <v>379.569482374099</v>
+        <v>379.1225176942713</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16489,28 +16629,28 @@
         <v>0.0893</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1423772033914974</v>
+        <v>0.1740300912925609</v>
       </c>
       <c r="J3" t="n">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="K3" t="n">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01324601004870973</v>
+        <v>0.01928587608532883</v>
       </c>
       <c r="M3" t="n">
-        <v>8.418781132982454</v>
+        <v>8.548566832276787</v>
       </c>
       <c r="N3" t="n">
-        <v>98.4904235020813</v>
+        <v>101.2658797854311</v>
       </c>
       <c r="O3" t="n">
-        <v>9.924234151917281</v>
+        <v>10.06309494069449</v>
       </c>
       <c r="P3" t="n">
-        <v>386.2956799665113</v>
+        <v>385.9804850503255</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16548,7 +16688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D523"/>
+  <dimension ref="A1:D528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28057,6 +28197,116 @@
         </is>
       </c>
     </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>-35.007296493848386,173.7769492570862</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>-35.00728264491587,173.7778490893699</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>-35.007292179761194,173.77694883415694</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>-35.00727482563763,173.77784832275535</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>-35.00729352791343,173.77694896632232</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>-35.00726952290867,173.77784780286737</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>-35.007288944195786,173.77694851696006</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>-35.00725927695782,173.77784679833832</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>-35.00729316840617,173.7769489310782</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>-35.00726008584867,173.77784687764324</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0047/nzd0047.xlsx
+++ b/data/nzd0047/nzd0047.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D528"/>
+  <dimension ref="A1:D531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9936,6 +9936,60 @@
       <c r="D528" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>413.69</v>
+      </c>
+      <c r="C529" t="n">
+        <v>411.79</v>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>413.57</v>
+      </c>
+      <c r="C530" t="n">
+        <v>412.46</v>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>413.88</v>
+      </c>
+      <c r="C531" t="n">
+        <v>413.09</v>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -9950,7 +10004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B643"/>
+  <dimension ref="A1:B647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16383,6 +16437,46 @@
       </c>
       <c r="B643" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -16551,28 +16645,28 @@
         <v>0.1827</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2575700644642678</v>
+        <v>0.2835207487532139</v>
       </c>
       <c r="J2" t="n">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="K2" t="n">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03586892366319272</v>
+        <v>0.04209474298835103</v>
       </c>
       <c r="M2" t="n">
-        <v>9.11578753087074</v>
+        <v>9.232377091956513</v>
       </c>
       <c r="N2" t="n">
-        <v>117.2519019826536</v>
+        <v>120.8444280717072</v>
       </c>
       <c r="O2" t="n">
-        <v>10.82829173889647</v>
+        <v>10.9929262742778</v>
       </c>
       <c r="P2" t="n">
-        <v>379.1225176942713</v>
+        <v>378.8632285028149</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16629,28 +16723,28 @@
         <v>0.0893</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1740300912925609</v>
+        <v>0.1944708633611315</v>
       </c>
       <c r="J3" t="n">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="K3" t="n">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01928587608532883</v>
+        <v>0.0236074681419528</v>
       </c>
       <c r="M3" t="n">
-        <v>8.548566832276787</v>
+        <v>8.635416523104848</v>
       </c>
       <c r="N3" t="n">
-        <v>101.2658797854311</v>
+        <v>103.3347428707233</v>
       </c>
       <c r="O3" t="n">
-        <v>10.06309494069449</v>
+        <v>10.16536978524261</v>
       </c>
       <c r="P3" t="n">
-        <v>385.9804850503255</v>
+        <v>385.7762448191957</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16688,7 +16782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D528"/>
+  <dimension ref="A1:D531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28307,6 +28401,72 @@
         </is>
       </c>
     </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>-35.007292808898896,173.77694889583415</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>-35.00725451348943,173.77784633132052</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>-35.0072938874207,173.77694900156644</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>-35.00724849174635,173.7778457409396</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>-35.00729110123939,173.77694872842466</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>-35.00724282951033,173.7778451858054</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0047/nzd0047.xlsx
+++ b/data/nzd0047/nzd0047.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D531"/>
+  <dimension ref="A1:D533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9990,6 +9990,42 @@
       <c r="D531" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>414.98</v>
+      </c>
+      <c r="C532" t="n">
+        <v>414.71</v>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>414.82</v>
+      </c>
+      <c r="C533" t="n">
+        <v>414.48</v>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -10004,7 +10040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B647"/>
+  <dimension ref="A1:B649"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16477,6 +16513,26 @@
       </c>
       <c r="B647" t="n">
         <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="n">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="n">
+        <v>-0.54</v>
       </c>
     </row>
   </sheetData>
@@ -16645,28 +16701,28 @@
         <v>0.1827</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2835207487532139</v>
+        <v>0.3012048798485629</v>
       </c>
       <c r="J2" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K2" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04209474298835103</v>
+        <v>0.04646506912770609</v>
       </c>
       <c r="M2" t="n">
-        <v>9.232377091956513</v>
+        <v>9.31256111109184</v>
       </c>
       <c r="N2" t="n">
-        <v>120.8444280717072</v>
+        <v>123.3834886144397</v>
       </c>
       <c r="O2" t="n">
-        <v>10.9929262742778</v>
+        <v>11.10781205343517</v>
       </c>
       <c r="P2" t="n">
-        <v>378.8632285028149</v>
+        <v>378.6858261633329</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16723,28 +16779,28 @@
         <v>0.0893</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1944708633611315</v>
+        <v>0.209154736437573</v>
       </c>
       <c r="J3" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K3" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0236074681419528</v>
+        <v>0.02686581208761529</v>
       </c>
       <c r="M3" t="n">
-        <v>8.635416523104848</v>
+        <v>8.699166550746009</v>
       </c>
       <c r="N3" t="n">
-        <v>103.3347428707233</v>
+        <v>105.0101270900564</v>
       </c>
       <c r="O3" t="n">
-        <v>10.16536978524261</v>
+        <v>10.24744490544137</v>
       </c>
       <c r="P3" t="n">
-        <v>385.7762448191957</v>
+        <v>385.6289402659348</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16782,7 +16838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D531"/>
+  <dimension ref="A1:D533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28467,6 +28523,50 @@
         </is>
       </c>
     </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>-35.007281214789536,173.77694775921202</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>-35.00722826947478,173.77784375831783</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>-35.00728265281861,173.77694790018836</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>-35.00723033664032,173.77784396098576</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
